--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127303976</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127303867</v>
       </c>
       <c r="B3" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127302582</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127303990</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127303976</v>
       </c>
       <c r="B2" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127303867</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127302582</v>
       </c>
       <c r="B4" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127303990</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127303976</v>
       </c>
       <c r="B2" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127303867</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127302582</v>
       </c>
       <c r="B4" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127303990</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127303976</v>
       </c>
       <c r="B2" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127303867</v>
       </c>
       <c r="B3" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127302582</v>
       </c>
       <c r="B4" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>127303990</v>
       </c>
       <c r="B5" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127303976</v>
+        <v>127302582</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478228</v>
+        <v>478187</v>
       </c>
       <c r="R2" t="n">
-        <v>6729511</v>
+        <v>6729402</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,6 +764,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127303867</v>
+        <v>127302723</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +825,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -833,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478283</v>
+        <v>478313</v>
       </c>
       <c r="R3" t="n">
-        <v>6729537</v>
+        <v>6729579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,6 +888,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På stor flat sten</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127302582</v>
+        <v>127303867</v>
       </c>
       <c r="B4" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478187</v>
+        <v>478283</v>
       </c>
       <c r="R4" t="n">
-        <v>6729402</v>
+        <v>6729537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,11 +1008,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127303990</v>
+        <v>127303976</v>
       </c>
       <c r="B5" t="n">
-        <v>56864</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,7 +1067,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1068,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478299</v>
+        <v>478228</v>
       </c>
       <c r="R5" t="n">
-        <v>6729464</v>
+        <v>6729511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,6 +1146,241 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127303990</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478299</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6729464</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127304031</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478342</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6729512</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sandbad</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127302723</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303976</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127303990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,8 +1411,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127304031</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127302582</v>
+        <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>92069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Dlr</t>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478187</v>
+        <v>478336</v>
       </c>
       <c r="R2" t="n">
-        <v>6729402</v>
+        <v>6729699</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,27 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>spillning</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,13 +786,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127302582</t>
+          <t>https://artportalen.se/Sighting/135883496</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127302723</v>
+        <v>127302582</v>
       </c>
       <c r="B3" t="n">
         <v>57141</v>
@@ -835,11 +822,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -852,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478313</v>
+        <v>478187</v>
       </c>
       <c r="R3" t="n">
-        <v>6729579</v>
+        <v>6729402</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På stor flat sten</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,13 +911,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127302723</t>
+          <t>https://artportalen.se/Sighting/127302582</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127303867</v>
+        <v>127302723</v>
       </c>
       <c r="B4" t="n">
         <v>57141</v>
@@ -964,7 +947,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -977,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478283</v>
+        <v>478313</v>
       </c>
       <c r="R4" t="n">
-        <v>6729537</v>
+        <v>6729579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,6 +1012,11 @@
           <t>11:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På stor flat sten</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1048,13 +1040,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127303867</t>
+          <t>https://artportalen.se/Sighting/127302723</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127303976</v>
+        <v>127303867</v>
       </c>
       <c r="B5" t="n">
         <v>57141</v>
@@ -1087,7 +1079,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1097,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478228</v>
+        <v>478283</v>
       </c>
       <c r="R5" t="n">
-        <v>6729511</v>
+        <v>6729537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1168,13 +1160,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127303976</t>
+          <t>https://artportalen.se/Sighting/127303867</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127303990</v>
+        <v>127303976</v>
       </c>
       <c r="B6" t="n">
         <v>57141</v>
@@ -1207,7 +1199,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1217,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478299</v>
+        <v>478228</v>
       </c>
       <c r="R6" t="n">
-        <v>6729464</v>
+        <v>6729511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,13 +1280,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127303990</t>
+          <t>https://artportalen.se/Sighting/127303976</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127304031</v>
+        <v>127303990</v>
       </c>
       <c r="B7" t="n">
         <v>57141</v>
@@ -1327,7 +1319,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1337,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478342</v>
+        <v>478299</v>
       </c>
       <c r="R7" t="n">
-        <v>6729512</v>
+        <v>6729464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,11 +1377,6 @@
           <t>11:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>sandbad</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1413,7 +1400,2370 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/127303990</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127304031</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478342</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6729512</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sandbad</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/127304031</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135882802</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478174</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6729450</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135882802</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135882853</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478166</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6729464</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135882853</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135882881</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478167</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6729466</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135882881</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135882953</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478169</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6729473</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135882953</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135882976</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478164</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6729535</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135882976</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135883080</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478236</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6729529</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883080</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135883138</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478248</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6729543</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883138</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135883224</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478275</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6729577</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883224</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135883333</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478356</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6729656</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883333</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135883405</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478367</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6729654</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883405</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135883545</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>478336</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6729699</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883545</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135883809</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>478235</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6729735</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883809</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135883959</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478222</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6729659</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135883959</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135884021</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>478201</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6729621</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135884021</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135884046</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>478164</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6729638</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135884046</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135884373</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>478151</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6729650</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135884373</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135884476</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>478152</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6729647</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135884476</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135884506</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>478165</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6729602</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135884506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135884571</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Småtjärnarna, Småtjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>478151</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6729530</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Siljansnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135884571</t>
         </is>
       </c>
     </row>
@@ -1425,6 +3775,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>135882802</v>
       </c>
       <c r="B9" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>135882853</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135882881</v>
       </c>
       <c r="B11" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135882953</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135882976</v>
       </c>
       <c r="B13" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135883080</v>
       </c>
       <c r="B14" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135883138</v>
       </c>
       <c r="B15" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135883224</v>
       </c>
       <c r="B16" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135883333</v>
       </c>
       <c r="B17" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135883405</v>
       </c>
       <c r="B18" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135883545</v>
       </c>
       <c r="B19" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135883809</v>
       </c>
       <c r="B20" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135883959</v>
       </c>
       <c r="B21" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135884021</v>
       </c>
       <c r="B22" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135884046</v>
       </c>
       <c r="B23" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135884373</v>
       </c>
       <c r="B24" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135884476</v>
       </c>
       <c r="B25" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135884506</v>
       </c>
       <c r="B26" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>135884571</v>
       </c>
       <c r="B27" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>135882802</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>135882853</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135882881</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135882953</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135882976</v>
       </c>
       <c r="B13" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135883080</v>
       </c>
       <c r="B14" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135883138</v>
       </c>
       <c r="B15" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135883224</v>
       </c>
       <c r="B16" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135883333</v>
       </c>
       <c r="B17" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135883405</v>
       </c>
       <c r="B18" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135883545</v>
       </c>
       <c r="B19" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135883809</v>
       </c>
       <c r="B20" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135883959</v>
       </c>
       <c r="B21" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135884021</v>
       </c>
       <c r="B22" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135884046</v>
       </c>
       <c r="B23" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135884373</v>
       </c>
       <c r="B24" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135884476</v>
       </c>
       <c r="B25" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135884506</v>
       </c>
       <c r="B26" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>135884571</v>
       </c>
       <c r="B27" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>135882802</v>
       </c>
       <c r="B9" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>135882853</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135882881</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135882953</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135882976</v>
       </c>
       <c r="B13" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135883080</v>
       </c>
       <c r="B14" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135883138</v>
       </c>
       <c r="B15" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135883224</v>
       </c>
       <c r="B16" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135883333</v>
       </c>
       <c r="B17" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135883405</v>
       </c>
       <c r="B18" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135883545</v>
       </c>
       <c r="B19" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135883809</v>
       </c>
       <c r="B20" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135883959</v>
       </c>
       <c r="B21" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135884021</v>
       </c>
       <c r="B22" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135884046</v>
       </c>
       <c r="B23" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135884373</v>
       </c>
       <c r="B24" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135884476</v>
       </c>
       <c r="B25" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135884506</v>
       </c>
       <c r="B26" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>135884571</v>
       </c>
       <c r="B27" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>135882802</v>
       </c>
       <c r="B9" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>135882853</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135882881</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135882953</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135882976</v>
       </c>
       <c r="B13" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135883080</v>
       </c>
       <c r="B14" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135883138</v>
       </c>
       <c r="B15" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135883224</v>
       </c>
       <c r="B16" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135883333</v>
       </c>
       <c r="B17" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135883405</v>
       </c>
       <c r="B18" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135883545</v>
       </c>
       <c r="B19" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135883809</v>
       </c>
       <c r="B20" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135883959</v>
       </c>
       <c r="B21" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135884021</v>
       </c>
       <c r="B22" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135884046</v>
       </c>
       <c r="B23" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135884373</v>
       </c>
       <c r="B24" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135884476</v>
       </c>
       <c r="B25" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135884506</v>
       </c>
       <c r="B26" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>135884571</v>
       </c>
       <c r="B27" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>135882802</v>
       </c>
       <c r="B9" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>135882853</v>
       </c>
       <c r="B10" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135882881</v>
       </c>
       <c r="B11" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135882953</v>
       </c>
       <c r="B12" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135882976</v>
       </c>
       <c r="B13" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135883080</v>
       </c>
       <c r="B14" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135883138</v>
       </c>
       <c r="B15" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135883224</v>
       </c>
       <c r="B16" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135883333</v>
       </c>
       <c r="B17" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135883405</v>
       </c>
       <c r="B18" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135883545</v>
       </c>
       <c r="B19" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135883809</v>
       </c>
       <c r="B20" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135883959</v>
       </c>
       <c r="B21" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135884021</v>
       </c>
       <c r="B22" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135884046</v>
       </c>
       <c r="B23" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135884373</v>
       </c>
       <c r="B24" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135884476</v>
       </c>
       <c r="B25" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135884506</v>
       </c>
       <c r="B26" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>135884571</v>
       </c>
       <c r="B27" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>135882802</v>
       </c>
       <c r="B9" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>135882853</v>
       </c>
       <c r="B10" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>135882881</v>
       </c>
       <c r="B11" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135882953</v>
       </c>
       <c r="B12" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135882976</v>
       </c>
       <c r="B13" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135883080</v>
       </c>
       <c r="B14" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>135883138</v>
       </c>
       <c r="B15" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135883224</v>
       </c>
       <c r="B16" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>135883333</v>
       </c>
       <c r="B17" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135883405</v>
       </c>
       <c r="B18" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135883545</v>
       </c>
       <c r="B19" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135883809</v>
       </c>
       <c r="B20" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135883959</v>
       </c>
       <c r="B21" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135884021</v>
       </c>
       <c r="B22" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>135884046</v>
       </c>
       <c r="B23" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135884373</v>
       </c>
       <c r="B24" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135884476</v>
       </c>
       <c r="B25" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135884506</v>
       </c>
       <c r="B26" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         <v>135884571</v>
       </c>
       <c r="B27" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 31951-2025 artfynd.xlsx
+++ b/artfynd/A 31951-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135883496</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
